--- a/example_files/example.xlsx
+++ b/example_files/example.xlsx
@@ -5,41 +5,64 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\86_大学アルバイト\06_副手\2026\オブジェクト指向プログラミング\演習投影学生指名プログラム\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\86_大学アルバイト\06_副手\2026\オブジェクト指向プログラミング\演習投影学生指名プログラム\example_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA5CC53-9DE9-428D-B65B-58CEA3B77B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43EFCB7-2955-4A68-823F-9C284C16B50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="4155" windowWidth="21600" windowHeight="11295" xr2:uid="{D3635CCA-119C-47BA-A50F-388A3324B038}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>学期</t>
+  </si>
+  <si>
+    <t>授業コード</t>
+  </si>
+  <si>
+    <t>科目コード</t>
+  </si>
+  <si>
+    <t>授業科目</t>
+  </si>
+  <si>
+    <t>授業科目（英語）</t>
+  </si>
+  <si>
+    <t>担当教員氏名</t>
+  </si>
+  <si>
+    <t>担当教員名＿カナ</t>
+  </si>
+  <si>
+    <t>担当教員氏名（英語）</t>
+  </si>
+  <si>
+    <t>開講区分</t>
+  </si>
+  <si>
+    <t>開講曜日</t>
+  </si>
+  <si>
+    <t>教室</t>
+  </si>
+  <si>
+    <t>前期</t>
+  </si>
+  <si>
+    <t>週間授業</t>
+  </si>
   <si>
     <t>学籍番号</t>
   </si>
@@ -47,19 +70,54 @@
     <t>学生氏名</t>
   </si>
   <si>
-    <t>学生氏名＿カナ</t>
+    <t>学生氏名＿英語</t>
+  </si>
+  <si>
+    <t>性別</t>
+  </si>
+  <si>
+    <t>学年</t>
+  </si>
+  <si>
+    <t>セメスタ</t>
+  </si>
+  <si>
+    <t>カリキュラム学科組織コード</t>
+  </si>
+  <si>
+    <t>カリキュラム学科</t>
+  </si>
+  <si>
+    <t>入学年度学期</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>男性</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2022年度 前期</t>
+  </si>
+  <si>
+    <t>2024年度 前期</t>
+  </si>
+  <si>
+    <t>女性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プログラミング </t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>11XX000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>22XX000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>33XX000</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>電大　太郎</t>
@@ -69,7 +127,15 @@
     <rPh sb="3" eb="5">
       <t>タロウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>デンダイ　タロウ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>22XX000</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>電大　花子</t>
@@ -79,25 +145,81 @@
     <rPh sb="3" eb="5">
       <t>ハナコ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>デンダイ　ハナコ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>33XX000</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>岡部　倫太郎</t>
     <rPh sb="3" eb="6">
       <t>リンタロウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デンダイ　タロウ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デンダイ　ハナコ</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>オカベ　リンタロウ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DENDAI TARO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DENDAI HANAKO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OKABE RINTARO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【神田】10号館0000教室</t>
+    <rPh sb="1" eb="3">
+      <t>カンダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月1</t>
+    <rPh sb="0" eb="1">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DENDAI, kyouin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デンダイ キョウイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電大 教員</t>
+    <rPh sb="0" eb="2">
+      <t>デンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Programming</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大学 工学部 工学科</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学生氏名＿カナ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -105,12 +227,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color indexed="8"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -144,9 +272,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,15 +615,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E38D1E5-A846-4D7E-BE84-6357B6DCA148}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,38 +643,231 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>3</v>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A2" s="1">
+        <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="1">
+        <v>9999999999</v>
+      </c>
+      <c r="D2" s="1">
+        <v>9999999999</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>5</v>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>9999999999</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2">
+        <v>999</v>
+      </c>
+      <c r="K4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
+        <v>9999999999</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2">
+        <v>999</v>
+      </c>
+      <c r="K5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>9999999999</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="2">
+        <v>999</v>
+      </c>
+      <c r="K6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
